--- a/Scrum_Template_Team-3.xlsx
+++ b/Scrum_Template_Team-3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\307420\Desktop\Mahesh-k8s-Manifest-Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\307420\Desktop\Mahesh-k8s-Manifest-Files\kubernetes-v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492913C3-C80A-44EA-929B-928634FACC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907A97B8-3141-41E0-BD01-061242C92590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="1100" windowWidth="14400" windowHeight="7270" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -417,9 +417,6 @@
     <t>Create Container and deployed image for monolithic application</t>
   </si>
   <si>
-    <t>Created custom network and deplyed microservices in multiple containers</t>
-  </si>
-  <si>
     <t xml:space="preserve">Containerized microservice application with services in two different network and initialized a gateway for communication </t>
   </si>
   <si>
@@ -502,6 +499,9 @@
   </si>
   <si>
     <t>Understanding the Kubernetes components, its architecture, how components communicate, api server, setting up our own clusters, deep diving into the workflow behind each command of creating control plane, pods and its life cycle.</t>
+  </si>
+  <si>
+    <t>Created custom network and deployed microservices in multiple containers</t>
   </si>
 </sst>
 </file>
@@ -2292,7 +2292,7 @@
         <v>46088</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2309,7 +2309,7 @@
         <v>46091</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -4212,7 +4212,7 @@
         <v>7</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>124</v>
@@ -4238,7 +4238,7 @@
         <v>7</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>124</v>
@@ -4264,7 +4264,7 @@
         <v>7</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>124</v>
@@ -4290,7 +4290,7 @@
         <v>7</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>124</v>
@@ -4316,7 +4316,7 @@
         <v>7</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>124</v>
@@ -4342,7 +4342,7 @@
         <v>7</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>124</v>
@@ -4372,10 +4372,10 @@
         <v>7</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>8</v>
@@ -4398,10 +4398,10 @@
         <v>7</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>12</v>
@@ -4424,10 +4424,10 @@
         <v>7</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>14</v>
@@ -4450,10 +4450,10 @@
         <v>7</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>15</v>
@@ -4476,10 +4476,10 @@
         <v>7</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>16</v>
@@ -4502,10 +4502,10 @@
         <v>7</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>17</v>
@@ -4532,10 +4532,10 @@
         <v>7</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>8</v>
@@ -4558,10 +4558,10 @@
         <v>7</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>12</v>
@@ -4584,10 +4584,10 @@
         <v>7</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>14</v>
@@ -4610,10 +4610,10 @@
         <v>7</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>15</v>
@@ -4636,10 +4636,10 @@
         <v>7</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>16</v>
@@ -4662,10 +4662,10 @@
         <v>7</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>17</v>
@@ -4692,10 +4692,10 @@
         <v>7</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>8</v>
@@ -4718,10 +4718,10 @@
         <v>7</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>12</v>
@@ -4744,10 +4744,10 @@
         <v>7</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>14</v>
@@ -4770,10 +4770,10 @@
         <v>7</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>15</v>
@@ -4796,10 +4796,10 @@
         <v>7</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>16</v>
@@ -4822,10 +4822,10 @@
         <v>7</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>17</v>
